--- a/Result/profitability/4951.xlsx
+++ b/Result/profitability/4951.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM46"/>
+  <dimension ref="A1:AM47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.3825</v>
+        <v>1.42625</v>
       </c>
       <c r="N2" t="n">
-        <v>70.67875000000001</v>
+        <v>71.4225</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>1.44875</v>
+        <v>1.48125</v>
       </c>
       <c r="N3" t="n">
-        <v>66.99249999999999</v>
+        <v>67.33125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.51</v>
       </c>
       <c r="M4" t="n">
-        <v>1.50875</v>
+        <v>1.5125</v>
       </c>
       <c r="N4" t="n">
-        <v>63.29125</v>
+        <v>63.16375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3675</v>
+        <v>1.36125</v>
       </c>
       <c r="N5" t="n">
-        <v>59.18375</v>
+        <v>59.0625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -6272,6 +6272,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4951</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>136</v>
+      </c>
+      <c r="D47" t="n">
+        <v>32</v>
+      </c>
+      <c r="E47" t="n">
+        <v>105</v>
+      </c>
+      <c r="F47" t="n">
+        <v>76.62</v>
+      </c>
+      <c r="G47" t="n">
+        <v>45</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>33.03%</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>47</v>
+      </c>
+      <c r="K47" t="n">
+        <v>44</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.36875</v>
+      </c>
+      <c r="N47" t="n">
+        <v>75.2825</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W47" t="n">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="X47" t="n">
+        <v>-0.2456140350877193</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.2000000000000028</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.002617115938235992</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-0.05000000000000004</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>-0.03731343283582089</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>-0.9699999999999989</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>-0.01250161103234948</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK47" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
